--- a/rules/CORE-000352/positive/01/data/unit-test-coreid-CG0207-positive.xlsx
+++ b/rules/CORE-000352/positive/01/data/unit-test-coreid-CG0207-positive.xlsx
@@ -537,7 +537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1409,6 +1409,159 @@
         <v>184</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>GUARD-SESEQ</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>SCREEN</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Screening</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2014-01-08</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>-7</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>GUARD-SESEQ</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Zanomaline 54 mg</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>TREATMENT</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2014-01-08</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2014-02-01</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>GUARD-SESEQ</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Zanomaline 81 mg</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>TREATMENT</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2014-02-01</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2014-03-01</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>18</v>
+      </c>
+      <c r="K20" t="n">
+        <v>169</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
